--- a/planilha_molde.xlsx
+++ b/planilha_molde.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabriel.tiara\Planilha Creator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEE04C7-FFFE-4020-A52E-DA63B9A93387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7EEE4E-FF5A-46B4-AF41-73EAAB4B8FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23880" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{DD2F1464-8338-49B3-8B60-C952B17A4EF4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
   <si>
     <t>ORDEM DE PRODUÇÃO</t>
   </si>
@@ -72,52 +72,13 @@
   </si>
   <si>
     <t>X</t>
-  </si>
-  <si>
-    <t>OPERADOR</t>
-  </si>
-  <si>
-    <t>TEMPO TOTAL DE PROCESSO ( MINUTOS )</t>
-  </si>
-  <si>
-    <t>SECCIONADORA</t>
-  </si>
-  <si>
-    <t>CNC NESTING</t>
-  </si>
-  <si>
-    <t>CNC ROVER / 5 EIXOS</t>
-  </si>
-  <si>
-    <t>MONTAGEM PRENSA</t>
-  </si>
-  <si>
-    <t>PRENSA</t>
-  </si>
-  <si>
-    <t>LAMINADORA</t>
-  </si>
-  <si>
-    <t>ELÉTRICA</t>
-  </si>
-  <si>
-    <t>LIXADEIRA / ESCOVA</t>
-  </si>
-  <si>
-    <t>MARCENEIRO</t>
-  </si>
-  <si>
-    <t>RESPONSÁVEL</t>
-  </si>
-  <si>
-    <t>OBSERVAÇÕES</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,11 +138,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial1"/>
     </font>
     <font>
@@ -205,7 +161,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -243,74 +199,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -324,37 +212,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -365,18 +227,12 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -389,80 +245,41 @@
     <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -816,36 +633,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="33" customHeight="1">
-      <c r="A1" s="26"/>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
+      <c r="A1" s="13"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
     </row>
     <row r="2" spans="1:13" ht="22.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
       <c r="L2" s="1" t="s">
         <v>2</v>
       </c>
@@ -853,49 +670,49 @@
     </row>
     <row r="3" spans="1:13" ht="22.5" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
       <c r="L3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
     </row>
     <row r="5" spans="1:13" ht="25.5" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
       <c r="I5" s="3" t="s">
         <v>6</v>
       </c>
@@ -905,7 +722,7 @@
       <c r="K5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="M5" s="3" t="s">
@@ -913,392 +730,120 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A6" s="13"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="13">
-        <v>0</v>
-      </c>
-      <c r="D6" s="13" t="s">
+      <c r="A6" s="7"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="7">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="13">
-        <v>0</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="E6" s="10"/>
+      <c r="F6" s="7">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="13">
-        <v>0</v>
-      </c>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="15"/>
+      <c r="H6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="9"/>
     </row>
     <row r="7" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A7" s="13"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="13">
-        <v>0</v>
-      </c>
-      <c r="D7" s="13" t="s">
+      <c r="A7" s="7"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="7">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="13">
-        <v>0</v>
-      </c>
-      <c r="G7" s="13" t="s">
+      <c r="E7" s="10"/>
+      <c r="F7" s="7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="13">
-        <v>0</v>
-      </c>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="15"/>
+      <c r="H7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="9"/>
     </row>
     <row r="8" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A8" s="13"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="13">
-        <v>0</v>
-      </c>
-      <c r="D8" s="13" t="s">
+      <c r="A8" s="16"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="16">
+        <v>0</v>
+      </c>
+      <c r="D8" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="13">
-        <v>0</v>
-      </c>
-      <c r="G8" s="13" t="s">
+      <c r="E8" s="17"/>
+      <c r="F8" s="16">
+        <v>0</v>
+      </c>
+      <c r="G8" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="13">
-        <v>0</v>
-      </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="15"/>
-    </row>
-    <row r="9" spans="1:13" ht="408.75" customHeight="1">
-      <c r="A9" s="33"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="35"/>
-    </row>
-    <row r="10" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A10" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="L10" s="31"/>
-      <c r="M10" s="32"/>
-    </row>
-    <row r="11" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A11" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="19"/>
-    </row>
-    <row r="12" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A12" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="19"/>
-    </row>
-    <row r="13" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A13" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="18"/>
-      <c r="M13" s="19"/>
-    </row>
-    <row r="14" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A14" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="19"/>
-    </row>
-    <row r="15" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A15" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="19"/>
-    </row>
-    <row r="16" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A16" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="19"/>
-    </row>
-    <row r="17" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A17" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-    </row>
-    <row r="18" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A18" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-    </row>
-    <row r="19" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A19" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="21"/>
-    </row>
-    <row r="20" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A20" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="37"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21"/>
-    </row>
-    <row r="21" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A21" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="27"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="27"/>
-      <c r="M21" s="27"/>
-    </row>
-    <row r="22" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A22" s="21"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
-    </row>
-    <row r="23" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A23" s="21"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="21"/>
-    </row>
-    <row r="24" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
-    </row>
+      <c r="H8" s="16">
+        <v>0</v>
+      </c>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="20"/>
+    </row>
+    <row r="9" spans="1:13" ht="44.25" customHeight="1">
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+    </row>
+    <row r="10" spans="1:13" ht="25.5" customHeight="1"/>
+    <row r="11" spans="1:13" ht="25.5" customHeight="1"/>
+    <row r="12" spans="1:13" ht="25.5" customHeight="1"/>
+    <row r="13" spans="1:13" ht="25.5" customHeight="1"/>
+    <row r="14" spans="1:13" ht="25.5" customHeight="1"/>
+    <row r="15" spans="1:13" ht="25.5" customHeight="1"/>
+    <row r="16" spans="1:13" ht="25.5" customHeight="1"/>
+    <row r="17" spans="10:10" ht="25.5" customHeight="1"/>
+    <row r="18" spans="10:10" ht="25.5" customHeight="1">
+      <c r="J18" s="22"/>
+    </row>
+    <row r="19" spans="10:10" ht="25.5" customHeight="1"/>
+    <row r="20" spans="10:10" ht="25.5" customHeight="1"/>
+    <row r="21" spans="10:10" ht="25.5" customHeight="1"/>
+    <row r="22" spans="10:10" ht="25.5" customHeight="1"/>
+    <row r="23" spans="10:10" ht="25.5" customHeight="1"/>
+    <row r="24" spans="10:10" ht="25.5" customHeight="1"/>
   </sheetData>
-  <mergeCells count="43">
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A24:M24"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="A21:M21"/>
-    <mergeCell ref="A22:M22"/>
-    <mergeCell ref="A23:M23"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="K19:M19"/>
+  <mergeCells count="6">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:M1"/>
     <mergeCell ref="B2:K3"/>
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="A9:M9"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/planilha_molde.xlsx
+++ b/planilha_molde.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabriel.tiara\Planilha Creator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7EEE4E-FF5A-46B4-AF41-73EAAB4B8FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F5DCF03-6906-4082-A629-D9168A73A75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23880" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{DD2F1464-8338-49B3-8B60-C952B17A4EF4}"/>
   </bookViews>
@@ -216,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -248,19 +248,6 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -276,10 +263,22 @@
     <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -633,36 +632,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="33" customHeight="1">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
+      <c r="A1" s="16"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="22.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
       <c r="L2" s="1" t="s">
         <v>2</v>
       </c>
@@ -670,49 +669,49 @@
     </row>
     <row r="3" spans="1:13" ht="22.5" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
       <c r="L3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
     </row>
     <row r="5" spans="1:13" ht="25.5" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
       <c r="I5" s="3" t="s">
         <v>6</v>
       </c>
@@ -780,31 +779,31 @@
       <c r="M7" s="9"/>
     </row>
     <row r="8" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="16">
-        <v>0</v>
-      </c>
-      <c r="D8" s="16" t="s">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="11">
+        <v>0</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="16">
-        <v>0</v>
-      </c>
-      <c r="G8" s="16" t="s">
+      <c r="E8" s="12"/>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="16">
-        <v>0</v>
-      </c>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="20"/>
+      <c r="H8" s="11">
+        <v>0</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="15"/>
     </row>
-    <row r="9" spans="1:13" ht="44.25" customHeight="1">
+    <row r="9" spans="1:13" ht="33" customHeight="1">
       <c r="A9" s="21"/>
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
@@ -826,24 +825,22 @@
     <row r="14" spans="1:13" ht="25.5" customHeight="1"/>
     <row r="15" spans="1:13" ht="25.5" customHeight="1"/>
     <row r="16" spans="1:13" ht="25.5" customHeight="1"/>
-    <row r="17" spans="10:10" ht="25.5" customHeight="1"/>
-    <row r="18" spans="10:10" ht="25.5" customHeight="1">
-      <c r="J18" s="22"/>
-    </row>
-    <row r="19" spans="10:10" ht="25.5" customHeight="1"/>
-    <row r="20" spans="10:10" ht="25.5" customHeight="1"/>
-    <row r="21" spans="10:10" ht="25.5" customHeight="1"/>
-    <row r="22" spans="10:10" ht="25.5" customHeight="1"/>
-    <row r="23" spans="10:10" ht="25.5" customHeight="1"/>
-    <row r="24" spans="10:10" ht="25.5" customHeight="1"/>
+    <row r="17" ht="25.5" customHeight="1"/>
+    <row r="18" ht="25.5" customHeight="1"/>
+    <row r="19" ht="25.5" customHeight="1"/>
+    <row r="20" ht="25.5" customHeight="1"/>
+    <row r="21" ht="25.5" customHeight="1"/>
+    <row r="22" ht="25.5" customHeight="1"/>
+    <row r="23" ht="25.5" customHeight="1"/>
+    <row r="24" ht="25.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A9:M9"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:M1"/>
     <mergeCell ref="B2:K3"/>
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="A9:M9"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/planilha_molde.xlsx
+++ b/planilha_molde.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabriel.tiara\Planilha Creator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F5DCF03-6906-4082-A629-D9168A73A75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6767E8D7-654D-4D3E-B016-D263BE2C8ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23880" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{DD2F1464-8338-49B3-8B60-C952B17A4EF4}"/>
   </bookViews>
@@ -263,6 +263,9 @@
     <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -275,9 +278,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -624,7 +624,7 @@
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="4.5703125" customWidth="1"/>
     <col min="8" max="8" width="8.140625" customWidth="1"/>
-    <col min="9" max="9" width="28.28515625" customWidth="1"/>
+    <col min="9" max="9" width="41.140625" customWidth="1"/>
     <col min="10" max="10" width="6.140625" customWidth="1"/>
     <col min="11" max="11" width="28.7109375" customWidth="1"/>
     <col min="12" max="12" width="21.7109375" customWidth="1"/>
@@ -632,36 +632,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="33" customHeight="1">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
+      <c r="A1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
     </row>
     <row r="2" spans="1:13" ht="22.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
       <c r="L2" s="1" t="s">
         <v>2</v>
       </c>
@@ -669,49 +669,49 @@
     </row>
     <row r="3" spans="1:13" ht="22.5" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
       <c r="L3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:13" ht="14.25" customHeight="1">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
     </row>
     <row r="5" spans="1:13" ht="25.5" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
       <c r="I5" s="3" t="s">
         <v>6</v>
       </c>
@@ -804,19 +804,19 @@
       <c r="M8" s="15"/>
     </row>
     <row r="9" spans="1:13" ht="33" customHeight="1">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="21"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
     </row>
     <row r="10" spans="1:13" ht="25.5" customHeight="1"/>
     <row r="11" spans="1:13" ht="25.5" customHeight="1"/>
